--- a/data/processed_data/Video_068_hw30/contracciones_Video_068_hw30.xlsx
+++ b/data/processed_data/Video_068_hw30/contracciones_Video_068_hw30.xlsx
@@ -981,7 +981,7 @@
         <v>3.669286739999987</v>
       </c>
       <c r="G2" t="n">
-        <v>1.259667676590838</v>
+        <v>1.259667676590754</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>

--- a/data/processed_data/Video_068_hw30/contracciones_Video_068_hw30.xlsx
+++ b/data/processed_data/Video_068_hw30/contracciones_Video_068_hw30.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,22 +418,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>umbral_px</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>eventos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>falsos_control</t>
         </is>
@@ -788,172 +776,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_frames</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>signo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ruido_canal_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ruido_grosor_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>k_usado</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>k_automatico</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>hay_meseta</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>meseta_motivo</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>meseta_k_rango</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>conteo_reportable</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>cinetica_grupo_principal</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>eventos_junto_al_borde</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>mesetas</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>motivo_no_reportable</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>ruido_borde_sup_px</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>ruido_borde_inf_px</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>cociente_ruido_bordes</t>
         </is>

--- a/data/processed_data/Video_068_hw30/contracciones_Video_068_hw30.xlsx
+++ b/data/processed_data/Video_068_hw30/contracciones_Video_068_hw30.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="estab_Video_068_hw30" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="resumen_Video_068_hw30" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="estab_Video_068_hw30" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumen_Video_068_hw30" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="basal_Video_068_hw30" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -772,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,6 +947,36 @@
           <t>cociente_ruido_bordes</t>
         </is>
       </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>basal_fin_s</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>basal_definicion</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_px</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_pct</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>basal_contable</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>basal_resumen</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1055,6 +1086,126 @@
       </c>
       <c r="AH2" t="n">
         <v>1.041250594388975</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0-10 s</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>6.971374999999995</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2.093134885461243</v>
+      </c>
+      <c r="AM2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>no contable (conteo NO reportable); actividad basal 2.09 % del grosor</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>dato</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>basal_fin_s</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>basal_definicion</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0-10 s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_px</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>6.971374999999995</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_pct</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2.0931348854612426</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>basal_contable</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>basal_resumen</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>no contable (conteo NO reportable); actividad basal 2.09 % del grosor</t>
+        </is>
       </c>
     </row>
   </sheetData>
